--- a/data/trans_orig/IP1009-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Estudios-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>688</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413828</t>
+          <t>413842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471447</t>
+          <t>471066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476314</t>
+          <t>476313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886884</t>
+          <t>886813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892381</t>
+          <t>892390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170515</t>
+          <t>170263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329018</t>
+          <t>328762</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>677318</t>
+          <t>676771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>716418</t>
+          <t>716406</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>721297</t>
+          <t>721293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1395700</t>
+          <t>1395541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401913</t>
+          <t>1401852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88242</t>
+          <t>88543</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172095</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>446489</t>
+          <t>446137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489308</t>
+          <t>488659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937699</t>
+          <t>937663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>701906</t>
+          <t>702348</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>744387</t>
+          <t>744386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1449310</t>
+          <t>1449299</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1454429</t>
+          <t>1453811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,96%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>466762</t>
+          <t>466423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>471835</t>
+          <t>471833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>482338</t>
+          <t>481927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488026</t>
+          <t>487998</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>951975</t>
+          <t>952511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959178</t>
+          <t>959122</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168200</t>
+          <t>168877</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357147</t>
+          <t>355900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>697209</t>
+          <t>698002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>703602</t>
+          <t>703765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>738112</t>
+          <t>737975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744170</t>
+          <t>744176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1438717</t>
+          <t>1438793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1446534</t>
+          <t>1446649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1009-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,74 +1065,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>448</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2245</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2248</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5925</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>474919</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>470791</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476311</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>415639</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>413842</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>413839</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,89%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>716</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>474919</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>471066</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476313</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1343</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886813</t>
+          <t>886911</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892390</t>
+          <t>892387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>173432</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>170263</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>171157</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,82%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>489</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>328762</t>
+          <t>328587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6206</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4250</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5568</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>719902</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>715768</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>721299</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>679940</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>676771</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>677326</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,84%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1082</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>719902</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>716406</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>721293</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1395541</t>
+          <t>1396139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1401852</t>
+          <t>1401912</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3346</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3354</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91224</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>88543</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>88535</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>249</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172100</t>
+          <t>172062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2673,87 +2673,87 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>637</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3563</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1257</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>491785</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>488672</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>650</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>449063</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>446137</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>446495</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>491785</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>488659</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1354</t>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>937663</t>
+          <t>937696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3124,47 +3124,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4580</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>746882</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>744361</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>705625</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>702348</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>702424</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>746882</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>744386</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1449299</t>
+          <t>1449278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6423</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1832</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5867</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4887</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,1%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6808</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -4384,74 +4384,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>486033</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>482312</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488068</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>470458</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>466423</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>471833</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>467403</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>471835</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,9%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>486033</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>481927</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>487998</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,85%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1402</t>
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952511</t>
+          <t>952340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959122</t>
+          <t>959462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3826</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3542</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3836</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4297</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>171950</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>168877</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>169161</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,56%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>528</t>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355900</t>
+          <t>356361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4962,102 +4962,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2585</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6369</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6869</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>5287</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>2566</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>10422</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -5070,107 +5070,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>742142</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>737923</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744128</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>701786</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>698002</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>703765</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>697794</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>703617</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>742142</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>737975</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744176</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,89%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1443928</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1438525</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1446743</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1443928</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1438793</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1446649</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
